--- a/data/1.2_Metadonnées/1.2.1_Itinéaires techniques Rapsodyn/191125_ITK_Metadata.xlsx
+++ b/data/1.2_Metadonnées/1.2.1_Itinéaires techniques Rapsodyn/191125_ITK_Metadata.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecorlouer\Documents\A_RAW_DATA_EPHESIS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN.RDS-PRET-0218\Desktop\Agrocampus Ouest\M2\Projet ingénieur\meteo_vs_rendement\data\1.2_Metadonnées\1.2.1_Itinéaires techniques Rapsodyn\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0239CEEA-2C4C-4D65-BFEA-F0A64EF7B86F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11700" tabRatio="908" firstSheet="27" activeTab="43"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="908" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ ME" sheetId="45" r:id="rId1"/>
@@ -58,10 +59,21 @@
     <sheet name="CH218_SYN" sheetId="43" r:id="rId44"/>
     <sheet name="PUI18_SYN" sheetId="44" r:id="rId45"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -175,11 +187,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,7 +477,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2"/>
@@ -473,7 +485,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -530,19 +541,18 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="7"/>
-    <cellStyle name="Normal 2" xfId="8"/>
-    <cellStyle name="Normal 2 2" xfId="1"/>
-    <cellStyle name="Normal 2 2 2" xfId="6"/>
-    <cellStyle name="Normal 2 3" xfId="4"/>
-    <cellStyle name="Normal 3" xfId="3"/>
-    <cellStyle name="Normal 3 2" xfId="5"/>
-    <cellStyle name="Normal 6" xfId="2"/>
+    <cellStyle name="Normal 10" xfId="7" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 2 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal 3 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Normal 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -824,68 +834,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="21.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>43794</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>43794</v>
       </c>
       <c r="C10" t="s">
@@ -899,43 +909,43 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41521</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>41838</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -943,99 +953,99 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>30</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>41697</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>30</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>41711</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>41711</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1043,47 +1053,47 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>41884</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>42182</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1091,96 +1101,96 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:3" ht="13" thickBot="1"/>
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>52</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <v>52</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="57">
         <v>42073</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="51">
         <v>42073</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+    </row>
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1189,137 +1199,137 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:W19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="19" width="11.42578125" style="1"/>
-    <col min="20" max="21" width="11.42578125" style="2"/>
-    <col min="22" max="23" width="11.42578125" style="1"/>
-    <col min="24" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="19" width="11.453125" style="1"/>
+    <col min="20" max="21" width="11.453125" style="2"/>
+    <col min="22" max="23" width="11.453125" style="1"/>
+    <col min="24" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>41892</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>42186</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:3" ht="13" thickBot="1"/>
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>42062</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+    </row>
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1328,47 +1338,47 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>41885</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>42204</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1376,13 +1386,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13" thickBot="1">
       <c r="B9" s="1">
         <v>1</v>
       </c>
@@ -1390,93 +1400,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>35</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <v>35</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="57">
         <v>42047</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="51">
         <v>42047</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="54">
+      <c r="B15" s="19"/>
+      <c r="C15" s="53">
         <v>42072</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1484,43 +1494,43 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41891</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42191</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1528,107 +1538,107 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>80</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42052</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>50</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>42062</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>42062</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <v>30</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="47">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="56">
+      <c r="B17" s="55">
         <v>42075</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="58">
         <v>42075</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1636,43 +1646,43 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41892</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42208</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1680,99 +1690,99 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>75</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>75</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>42090</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="58">
         <v>42090</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42109</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1780,44 +1790,44 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41884</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42212</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1825,12 +1835,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="B9">
         <v>1</v>
       </c>
@@ -1838,93 +1848,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>50</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42055</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>50</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>42076</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>42076</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1932,47 +1942,47 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="20" width="11.42578125" style="1"/>
-    <col min="21" max="22" width="11.42578125" style="2"/>
-    <col min="23" max="25" width="11.42578125" style="1"/>
-    <col min="26" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="20" width="11.453125" style="1"/>
+    <col min="21" max="22" width="11.453125" style="2"/>
+    <col min="23" max="25" width="11.453125" style="1"/>
+    <col min="26" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>41886</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>42193</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1980,104 +1990,104 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:3" ht="13" thickBot="1"/>
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>60</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <v>30</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="57">
         <v>42054</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="51">
         <v>42054</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>30</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <v>42076</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="53">
         <v>42076</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2085,137 +2095,137 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:W19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="19" width="11.42578125" style="1"/>
-    <col min="20" max="21" width="11.42578125" style="2"/>
-    <col min="22" max="23" width="11.42578125" style="1"/>
-    <col min="24" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="19" width="11.453125" style="1"/>
+    <col min="20" max="21" width="11.453125" style="2"/>
+    <col min="22" max="23" width="11.453125" style="1"/>
+    <col min="24" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>42256</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>42562</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:3" ht="13" thickBot="1"/>
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>42429</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+    </row>
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2224,138 +2234,138 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42633</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42640</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42911</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42795</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2363,47 +2373,47 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>40429</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>40703</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2411,13 +2421,13 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13" thickBot="1">
       <c r="B9" s="1">
         <v>1</v>
       </c>
@@ -2425,93 +2435,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>30</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>40590</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>30</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <v>40612</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="53">
         <v>40612</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2520,142 +2530,142 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42633</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42640</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42913</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42795</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42808</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2663,43 +2673,43 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42612</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42923</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2707,95 +2717,95 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42802</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>72</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42810</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2804,44 +2814,44 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" style="4"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="19" max="19" width="11.453125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:19">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42618</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42920</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2850,98 +2860,98 @@
       </c>
       <c r="S6"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19">
       <c r="S7"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:19">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:19" ht="15" thickBot="1"/>
+    <row r="10" spans="1:19" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:19" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:19">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:19" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42786</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:19">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:19" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42810</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:19">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2949,47 +2959,47 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="20" width="11.42578125" style="1"/>
-    <col min="21" max="22" width="11.42578125" style="2"/>
-    <col min="23" max="27" width="11.42578125" style="1"/>
-    <col min="28" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="20" width="11.453125" style="1"/>
+    <col min="21" max="22" width="11.453125" style="2"/>
+    <col min="23" max="27" width="11.453125" style="1"/>
+    <col min="28" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>42636</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>42911</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -2997,92 +3007,92 @@
         <v>112.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:3" ht="13" thickBot="1"/>
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="63">
+      <c r="B12" s="40"/>
+      <c r="C12" s="61">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>42794</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+    </row>
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3091,142 +3101,142 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42614</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42624</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42924</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42804</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42811</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3234,142 +3244,142 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42613</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42623</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42935</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42797</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42810</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3377,156 +3387,156 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42614</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42620</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42935</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>67</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>177</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>45</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>42783</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="58">
         <v>42783</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>22</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>42793</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>42793</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47">
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="59">
+      <c r="B17" s="49"/>
+      <c r="C17" s="58">
         <v>42809</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="60">
+      <c r="B19" s="23"/>
+      <c r="C19" s="59">
         <v>42819</v>
       </c>
     </row>
@@ -3536,142 +3546,142 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42627</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42634</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42926</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42804</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42811</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3679,142 +3689,142 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42620</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42635</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42936</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="15" t="s">
+    <row r="8" spans="1:3" ht="15" thickBot="1"/>
+    <row r="9" spans="1:3" ht="15" thickBot="1">
+      <c r="A9" s="16"/>
+      <c r="B9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>0</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="46" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="48">
+      <c r="B11" s="46"/>
+      <c r="C11" s="47">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+    <row r="12" spans="1:3" ht="15" thickBot="1">
+      <c r="A12" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="59">
+      <c r="B12" s="49"/>
+      <c r="C12" s="58">
         <v>42786</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="23">
+      <c r="B13" s="21"/>
+      <c r="C13" s="22">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="38" t="s">
+    <row r="14" spans="1:3" ht="15" thickBot="1">
+      <c r="A14" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="60">
+      <c r="B14" s="23"/>
+      <c r="C14" s="59">
         <v>42817</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="46" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="48"/>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="49" t="s">
+      <c r="B15" s="46"/>
+      <c r="C15" s="47"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1">
+      <c r="A16" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="39" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="38" t="s">
+      <c r="B17" s="27"/>
+      <c r="C17" s="28"/>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1">
+      <c r="A18" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3822,142 +3832,142 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42615</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42622</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42934</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42789</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42816</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3965,47 +3975,47 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>40435</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>40725</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -4013,13 +4023,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13" thickBot="1">
       <c r="B9" s="1">
         <v>1</v>
       </c>
@@ -4027,93 +4037,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>40</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>40581</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>40</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <v>40612</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="53">
         <v>40612</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4121,43 +4131,43 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42613</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42936</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -4165,99 +4175,99 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>80</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>40</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42783</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>40</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42811</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4265,140 +4275,140 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42605</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42951</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>105</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>185</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>50</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42786</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>55</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42808</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4406,43 +4416,43 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42616</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>42928</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -4450,95 +4460,95 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>42783</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="62">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>42811</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4546,43 +4556,43 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42978</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43288</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -4590,96 +4600,96 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <f>82+68</f>
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>43165</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>43183</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4688,43 +4698,43 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42970</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43291</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -4732,85 +4742,85 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4818,47 +4828,47 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="20" width="11.42578125" style="1"/>
-    <col min="21" max="22" width="11.42578125" style="2"/>
-    <col min="23" max="27" width="11.42578125" style="1"/>
-    <col min="28" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="20" width="11.453125" style="1"/>
+    <col min="21" max="22" width="11.453125" style="2"/>
+    <col min="23" max="27" width="11.453125" style="1"/>
+    <col min="28" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>42989</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>43290</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -4866,92 +4876,92 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="9" spans="1:3" ht="13" thickBot="1"/>
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>43164</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-    </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+    </row>
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+    </row>
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4959,136 +4969,136 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42977</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42984</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43291</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>63</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>63</v>
       </c>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43167</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5096,46 +5106,46 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42977</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42984</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43291</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -5143,99 +5153,99 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>40</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>40</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43157</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="58">
         <v>43157</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22">
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>43180</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5243,136 +5253,136 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42982</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42988</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43298</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>30</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>30</v>
       </c>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43156</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5380,132 +5390,132 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42979</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42988</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43290</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5513,47 +5523,47 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>40800</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>40740</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -5561,13 +5571,13 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13" thickBot="1">
       <c r="B9" s="1">
         <v>0</v>
       </c>
@@ -5575,89 +5585,89 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>40960</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="54">
+      <c r="B15" s="19"/>
+      <c r="C15" s="53">
         <v>40982</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5665,43 +5675,43 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42982</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43297</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -5709,85 +5719,85 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>0</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5795,43 +5805,43 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42975</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43291</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -5839,89 +5849,89 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>81</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>81</v>
       </c>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43178</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5929,136 +5939,136 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42972</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>42979</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43305</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>55</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>55</v>
       </c>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43150</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6066,43 +6076,43 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42975</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43300</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6110,87 +6120,87 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>170</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43166</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="B15" s="23"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6198,43 +6208,43 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42975</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43301</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6242,93 +6252,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>40</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>20</v>
       </c>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43175</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>20</v>
       </c>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>43186</v>
       </c>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6336,43 +6346,43 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
   <sheetPr>
     <tabColor theme="8"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>42968</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>43295</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6380,93 +6390,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>95</v>
       </c>
-      <c r="C11" s="31"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+      <c r="C11" s="30"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>50</v>
       </c>
-      <c r="C12" s="48"/>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+      <c r="C12" s="47"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>43141</v>
       </c>
-      <c r="C13" s="51"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="C13" s="50"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>45</v>
       </c>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>43164</v>
       </c>
-      <c r="C15" s="25"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6474,47 +6484,47 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF33CCCC"/>
   </sheetPr>
   <dimension ref="A1:Y19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="25" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="25" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>41157</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>41470</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6545,7 +6555,7 @@
       <c r="X6"/>
       <c r="Y6"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
@@ -6572,12 +6582,12 @@
       <c r="X7"/>
       <c r="Y7"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="15" thickBot="1">
       <c r="B9" s="1">
         <v>0</v>
       </c>
@@ -6585,89 +6595,89 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:25" ht="15" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:25" ht="15" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:25">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="42">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:25" ht="15" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="52">
+      <c r="B13" s="43"/>
+      <c r="C13" s="51">
         <v>41330</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:25">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:25" ht="15" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="54">
+      <c r="B15" s="19"/>
+      <c r="C15" s="53">
         <v>41361</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:25">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="43" t="s">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="45"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6676,47 +6686,47 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
-    <col min="2" max="18" width="11.42578125" style="1"/>
-    <col min="19" max="20" width="11.42578125" style="2"/>
-    <col min="21" max="22" width="11.42578125" style="1"/>
-    <col min="23" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
+    <col min="2" max="18" width="11.453125" style="1"/>
+    <col min="19" max="20" width="11.453125" style="2"/>
+    <col min="21" max="22" width="11.453125" style="1"/>
+    <col min="23" max="16384" width="11.453125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="55">
+      <c r="B3" s="54">
         <v>41164</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>41491</v>
       </c>
     </row>
-    <row r="6" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" customFormat="1" ht="14.5">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6724,13 +6734,13 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" customFormat="1" ht="14.5"/>
+    <row r="8" spans="1:3" ht="13">
       <c r="A8" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13" thickBot="1">
       <c r="B9" s="1">
         <v>2</v>
       </c>
@@ -6738,101 +6748,101 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+    <row r="11" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A11" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>120</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="40" t="s">
+    <row r="12" spans="1:3" ht="13">
+      <c r="A12" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <v>50</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="41">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="57">
         <v>41319</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="51">
         <v>41319</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:3" ht="13">
+      <c r="A14" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>70</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <v>41347</v>
       </c>
-      <c r="C15" s="54">
+      <c r="C15" s="53">
         <v>41347</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" ht="13">
+      <c r="A16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="42">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+    <row r="17" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="52">
+      <c r="B17" s="43"/>
+      <c r="C17" s="51">
         <v>41378</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="35" t="s">
+    <row r="18" spans="1:3" ht="13">
+      <c r="A18" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-    </row>
-    <row r="19" spans="1:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+    </row>
+    <row r="19" spans="1:3" ht="13.5" thickBot="1">
+      <c r="A19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6840,43 +6850,43 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41520</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>41822</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -6884,12 +6894,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="B9">
         <v>1</v>
       </c>
@@ -6897,93 +6907,93 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>40</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="48">
+      <c r="B12" s="46"/>
+      <c r="C12" s="47">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="59">
+      <c r="B13" s="49"/>
+      <c r="C13" s="58">
         <v>41687</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>40</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>41713</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>41713</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6991,43 +7001,43 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41521</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>41837</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -7035,12 +7045,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="B9">
         <v>2</v>
       </c>
@@ -7048,103 +7058,103 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>80</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>50</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="56">
+      <c r="B13" s="55">
         <v>41697</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="58">
         <v>41697</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>0</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="60">
+      <c r="B15" s="23"/>
+      <c r="C15" s="59">
         <v>41705</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <v>30</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="47">
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="56">
+      <c r="B17" s="55">
         <v>41713</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="58">
         <v>41713</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7152,43 +7162,43 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>41522</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>41852</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -7196,12 +7206,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15" thickBot="1">
       <c r="B9">
         <v>2</v>
       </c>
@@ -7209,97 +7219,97 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="15" t="s">
+    <row r="10" spans="1:3" ht="15" thickBot="1">
+      <c r="A10" s="16"/>
+      <c r="B10" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:3" ht="15" thickBot="1">
+      <c r="A11" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>50</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>30</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="47">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:3" ht="15" thickBot="1">
+      <c r="A13" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="60">
         <v>41711</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="58">
         <v>41711</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>20</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="22">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1">
+      <c r="A15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="56">
         <v>41729</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="59">
         <v>41729</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+    <row r="16" spans="1:3">
+      <c r="A16" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="48"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1">
+      <c r="A17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1">
+      <c r="A19" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
